--- a/data/synopses_retry_broadway.xlsx
+++ b/data/synopses_retry_broadway.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Lackawanna Blues: no plot (438w); Lackawanna Blues (play): missing; Lackawanna Blues (film): plot via heading: Premise (482w)</t>
+          <t>Lackawanna Blues: no plot (438w); Lackawanna Blues (play): missing (search hits: ['Ruben Santiago-Hudson', 'S. Epatha Merkerson', 'List of black Tony Award winners and nominees']); Lackawanna Blues (film): plot via heading: Premise (482w)</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Is This a Room: missing; Is This a Room (play): missing</t>
+          <t>Is This a Room: missing (search hits: ['Room (play)', "Hell's Kitchen (musical)", 'The Room']); Is This a Room (play): missing (search hits: ['Room (play)', 'Chicago (play)', 'Room Service (play)'])</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Walking with Ghosts: missing</t>
+          <t>Walking with Ghosts: missing (search hits: ['Ghost (disambiguation)', 'Heathers: The Musical', 'List of Ghosts (American TV series) episodes'])</t>
         </is>
       </c>
     </row>
@@ -1392,72 +1392,27 @@
       <c r="C20" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>stage page</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>A Wonderful World (musical)</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/A_Wonderful_World_(musical)</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>heading: Act 1 (+1 sub)</t>
-        </is>
-      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="n">
-        <v>237</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>"Basin Street Blues" / "Bourbon Street Parade" - Company
-"Kiss of Fire" - Louis, Daisy
-"It's Tight Like That" - King Joe Oliver, Louis, Daisy, Ensemble
-"Kiss of Fire" (reprise) - Daisy
-"Up a Lazy River" - Banjo Ben
-"Avalon" - Louis and Company
-"Black and Blue" - Louis, Daisy, Lil, Alpha, Lucille
-"It Don't Mean a Thing" - King Joe Oliver, Ensemble
-"Do You Know What It Means to Miss New Orleans?" - King Joe Oliver, Louis
-"Got a Bran' New Suit" - Lil, Louis, King Joe Oliver
-"A Kiss to Build a Dream On" - Lil, Louis
-"Heebie Jeebies" - Louis, Lil, Ensemble
-"Dinah" - Louis
-"Tiger Rag" - Louis, Lil, Ensemble
-"You Rascal You" - Louis, Ensemble
-"Some of These Days" / "After You've Gone" - Lil, Daisy
-Act 2.
-"Oh, When The Saints Go Marching In" - Louis, Crooner
-"Big Butter and Egg Man" - Alpha, Louis
-"When You're Smiling" - Louis, Lincoln Perry, Ensemble
-"Do You Know What It Means to Miss New Orleans?" - King Joe Oliver
-"Ain't No Sweet Man That's Worth the Salt of My Tears" - Alpha
-"I Double Dare You" - Lucille, Ensemble
-"Cheek to Cheek" - Louis, Lucille
-"That's My Home" - Lucille
-"Back O'Town Blues" - Louis
-"Star Spangled Banner" - Louis
-"Hello, Dolly" - Louis
-"St. James Infirmary" - Daisy, Lil, Alpha, Lucille
-"What a Wonderful World" - Louis, Daisy, Lil, Alpha, Lucille, Company</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>[A Wonderful World (musical)] ##Production history; ###Miami New Drama (2020–2021); ###New Orleans and Chicago (2022–2023); ###Broadway (2024); ##Original cast and characters; ##Musical numbers; ###Act 1; ###Act 2; ##Award and nomination; ##References; ##External links</t>
+        </is>
+      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>A Wonderful World (musical): plot via heading: Act 1 (+1 sub) (694w)</t>
+          <t>A Wonderful World (musical): no plot (694w)</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1743,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Titaníque: missing; Titanique: no plot (1394w)</t>
+          <t>Titaníque: missing (search hits: ['Titanique', 'Marla Mindelle', 'Véronique Claveau']); Titanique: no plot (1394w)</t>
         </is>
       </c>
     </row>
